--- a/ro_workstation/data/mis/archive/20260428.xlsx
+++ b/ro_workstation/data/mis/archive/20260428.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Daily_MIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13F44DB-F2D1-4631-820F-3E3906684D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -152,7 +152,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="0000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,8 +161,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1" tint="4.9989318521683403E-2"/>
+      <color theme="1" tint="0.0499899983406067"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -192,37 +198,130 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -496,16 +595,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AM57"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="19" max="19" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.8571428571429" style="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7142857142857" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -624,7 +723,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:39" ht="15">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -680,7 +779,7 @@
         <v>18.370834291999998</v>
       </c>
       <c r="S2" s="4">
-        <v>6.1958381999999992E-2</v>
+        <v>0.061958381999999992</v>
       </c>
       <c r="T2" s="4">
         <v>30.010468885000002</v>
@@ -743,7 +842,7 @@
         <v>0.1950231</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:39" ht="15">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -832,16 +931,16 @@
         <v>0</v>
       </c>
       <c r="AD3" s="1">
-        <v>19.97</v>
+        <v>19.969999999999999</v>
       </c>
       <c r="AE3" s="1">
-        <v>64.22</v>
+        <v>64.219999999999999</v>
       </c>
       <c r="AF3" s="1">
         <v>87</v>
       </c>
       <c r="AG3" s="1">
-        <v>-22.78</v>
+        <v>-22.780000000000001</v>
       </c>
       <c r="AH3" s="1">
         <v>0</v>
@@ -862,7 +961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:39" ht="15">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -954,13 +1053,13 @@
         <v>10.42</v>
       </c>
       <c r="AE4" s="1">
-        <v>46.97</v>
+        <v>46.969999999999999</v>
       </c>
       <c r="AF4" s="1">
         <v>35</v>
       </c>
       <c r="AG4" s="1">
-        <v>11.97</v>
+        <v>11.970000000000001</v>
       </c>
       <c r="AH4" s="1">
         <v>0</v>
@@ -981,7 +1080,7 @@
         <v>0.62446000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:39" ht="15">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1061,7 +1160,7 @@
         <v>9284.7746318999998</v>
       </c>
       <c r="AA5" s="1">
-        <v>60.31</v>
+        <v>60.310000000000002</v>
       </c>
       <c r="AB5" s="1">
         <v>0</v>
@@ -1070,10 +1169,10 @@
         <v>0</v>
       </c>
       <c r="AD5" s="1">
-        <v>8.1</v>
+        <v>8.0999999999999996</v>
       </c>
       <c r="AE5" s="1">
-        <v>68.41</v>
+        <v>68.409999999999997</v>
       </c>
       <c r="AF5" s="1">
         <v>45</v>
@@ -1100,7 +1199,7 @@
         <v>0.47975000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:39" ht="15">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1180,7 +1279,7 @@
         <v>8720.3924537000003</v>
       </c>
       <c r="AA6" s="1">
-        <v>26.39</v>
+        <v>26.390000000000001</v>
       </c>
       <c r="AB6" s="1">
         <v>0</v>
@@ -1189,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="AD6" s="1">
-        <v>9.31</v>
+        <v>9.3100000000000005</v>
       </c>
       <c r="AE6" s="1">
         <v>35.700000000000003</v>
@@ -1198,7 +1297,7 @@
         <v>50</v>
       </c>
       <c r="AG6" s="1">
-        <v>-14.3</v>
+        <v>-14.300000000000001</v>
       </c>
       <c r="AH6" s="1">
         <v>0</v>
@@ -1219,7 +1318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:39" ht="15">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1299,7 +1398,7 @@
         <v>6444.0378168999996</v>
       </c>
       <c r="AA7" s="1">
-        <v>50.67</v>
+        <v>50.670000000000002</v>
       </c>
       <c r="AB7" s="1">
         <v>0</v>
@@ -1311,13 +1410,13 @@
         <v>1.2</v>
       </c>
       <c r="AE7" s="1">
-        <v>51.87</v>
+        <v>51.869999999999997</v>
       </c>
       <c r="AF7" s="1">
         <v>45</v>
       </c>
       <c r="AG7" s="1">
-        <v>6.87</v>
+        <v>6.8700000000000001</v>
       </c>
       <c r="AH7" s="1">
         <v>0</v>
@@ -1326,7 +1425,7 @@
         <v>36.983033599999999</v>
       </c>
       <c r="AJ7" s="1">
-        <v>6.9999999999999994E-5</v>
+        <v>6.9999999999999994E-05</v>
       </c>
       <c r="AK7" s="1">
         <v>0</v>
@@ -1335,10 +1434,10 @@
         <v>0</v>
       </c>
       <c r="AM7" s="1">
-        <v>6.9999999999999994E-5</v>
+        <v>6.9999999999999994E-05</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:39" ht="15">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1427,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="AD8" s="1">
-        <v>5.92</v>
+        <v>5.9199999999999999</v>
       </c>
       <c r="AE8" s="1">
         <v>22</v>
@@ -1445,7 +1544,7 @@
         <v>33.621761300000003</v>
       </c>
       <c r="AJ8" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>1.0000000000000001E-05</v>
       </c>
       <c r="AK8" s="1">
         <v>0</v>
@@ -1454,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="AM8" s="1">
-        <v>1.0000000000000001E-5</v>
+        <v>1.0000000000000001E-05</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:39" ht="15">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1549,13 +1648,13 @@
         <v>2.77</v>
       </c>
       <c r="AE9" s="1">
-        <v>42.97</v>
+        <v>42.969999999999999</v>
       </c>
       <c r="AF9" s="1">
         <v>40</v>
       </c>
       <c r="AG9" s="1">
-        <v>2.97</v>
+        <v>2.9700000000000002</v>
       </c>
       <c r="AH9" s="1">
         <v>0</v>
@@ -1564,7 +1663,7 @@
         <v>41.724883800000001</v>
       </c>
       <c r="AJ9" s="1">
-        <v>9.6699999999999998E-3</v>
+        <v>0.0096699999999999998</v>
       </c>
       <c r="AK9" s="1">
         <v>0</v>
@@ -1573,10 +1672,10 @@
         <v>0</v>
       </c>
       <c r="AM9" s="1">
-        <v>9.6699999999999998E-3</v>
+        <v>0.0096699999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:39" ht="15">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1656,7 +1755,7 @@
         <v>15714.0058995</v>
       </c>
       <c r="AA10" s="1">
-        <v>90.57</v>
+        <v>90.569999999999993</v>
       </c>
       <c r="AB10" s="1">
         <v>17.25</v>
@@ -1665,16 +1764,16 @@
         <v>0</v>
       </c>
       <c r="AD10" s="1">
-        <v>27.19</v>
+        <v>27.190000000000001</v>
       </c>
       <c r="AE10" s="1">
-        <v>135.01</v>
+        <v>135.00999999999999</v>
       </c>
       <c r="AF10" s="1">
         <v>80</v>
       </c>
       <c r="AG10" s="1">
-        <v>55.01</v>
+        <v>55.009999999999998</v>
       </c>
       <c r="AH10" s="1">
         <v>0</v>
@@ -1695,7 +1794,7 @@
         <v>14.36561</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:39" ht="15">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1775,7 +1874,7 @@
         <v>10226.941333999999</v>
       </c>
       <c r="AA11" s="1">
-        <v>592.29</v>
+        <v>592.28999999999996</v>
       </c>
       <c r="AB11" s="1">
         <v>0</v>
@@ -1787,13 +1886,13 @@
         <v>21.25</v>
       </c>
       <c r="AE11" s="1">
-        <v>613.54</v>
+        <v>613.53999999999996</v>
       </c>
       <c r="AF11" s="1">
         <v>70</v>
       </c>
       <c r="AG11" s="1">
-        <v>543.54</v>
+        <v>543.53999999999996</v>
       </c>
       <c r="AH11" s="1">
         <v>0</v>
@@ -1814,7 +1913,7 @@
         <v>1.1543399999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:39" ht="15">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1903,10 +2002,10 @@
         <v>0</v>
       </c>
       <c r="AD12" s="1">
-        <v>5.76</v>
+        <v>5.7599999999999998</v>
       </c>
       <c r="AE12" s="1">
-        <v>20.6</v>
+        <v>20.600000000000001</v>
       </c>
       <c r="AF12" s="1">
         <v>35</v>
@@ -1933,7 +2032,7 @@
         <v>2.18662</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:39" ht="15">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -2013,7 +2112,7 @@
         <v>4655.5189736000002</v>
       </c>
       <c r="AA13" s="1">
-        <v>36.74</v>
+        <v>36.740000000000002</v>
       </c>
       <c r="AB13" s="1">
         <v>0</v>
@@ -2025,13 +2124,13 @@
         <v>13.23</v>
       </c>
       <c r="AE13" s="1">
-        <v>49.97</v>
+        <v>49.969999999999999</v>
       </c>
       <c r="AF13" s="1">
         <v>30</v>
       </c>
       <c r="AG13" s="1">
-        <v>19.97</v>
+        <v>19.969999999999999</v>
       </c>
       <c r="AH13" s="1">
         <v>0</v>
@@ -2040,7 +2139,7 @@
         <v>25.048637100000001</v>
       </c>
       <c r="AJ13" s="1">
-        <v>5.0000000000000001E-4</v>
+        <v>0.00050000000000000001</v>
       </c>
       <c r="AK13" s="1">
         <v>0</v>
@@ -2049,10 +2148,10 @@
         <v>0</v>
       </c>
       <c r="AM13" s="1">
-        <v>5.0000000000000001E-4</v>
+        <v>0.00050000000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:39" ht="15">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -2132,10 +2231,10 @@
         <v>4221.9526538999999</v>
       </c>
       <c r="AA14" s="1">
-        <v>26.36</v>
+        <v>26.359999999999999</v>
       </c>
       <c r="AB14" s="1">
-        <v>6.49</v>
+        <v>6.4900000000000002</v>
       </c>
       <c r="AC14" s="1">
         <v>0</v>
@@ -2144,13 +2243,13 @@
         <v>0</v>
       </c>
       <c r="AE14" s="1">
-        <v>32.85</v>
+        <v>32.850000000000001</v>
       </c>
       <c r="AF14" s="1">
         <v>30</v>
       </c>
       <c r="AG14" s="1">
-        <v>2.85</v>
+        <v>2.8500000000000001</v>
       </c>
       <c r="AH14" s="1">
         <v>0</v>
@@ -2159,7 +2258,7 @@
         <v>23.0854809</v>
       </c>
       <c r="AJ14" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
       <c r="AK14" s="1">
         <v>0</v>
@@ -2168,10 +2267,10 @@
         <v>0</v>
       </c>
       <c r="AM14" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:39" ht="15">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -2260,10 +2359,10 @@
         <v>0</v>
       </c>
       <c r="AD15" s="1">
-        <v>5.34</v>
+        <v>5.3399999999999999</v>
       </c>
       <c r="AE15" s="1">
-        <v>34.36</v>
+        <v>34.359999999999999</v>
       </c>
       <c r="AF15" s="1">
         <v>30</v>
@@ -2278,7 +2377,7 @@
         <v>30.172422399999999</v>
       </c>
       <c r="AJ15" s="1">
-        <v>8.1999999999999998E-4</v>
+        <v>0.00081999999999999998</v>
       </c>
       <c r="AK15" s="1">
         <v>0</v>
@@ -2287,10 +2386,10 @@
         <v>0</v>
       </c>
       <c r="AM15" s="1">
-        <v>8.1999999999999998E-4</v>
+        <v>0.00081999999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:39" ht="15">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -2370,7 +2469,7 @@
         <v>12296.310953600001</v>
       </c>
       <c r="AA16" s="1">
-        <v>20.04</v>
+        <v>20.039999999999999</v>
       </c>
       <c r="AB16" s="1">
         <v>0</v>
@@ -2379,16 +2478,16 @@
         <v>0</v>
       </c>
       <c r="AD16" s="1">
-        <v>6.34</v>
+        <v>6.3399999999999999</v>
       </c>
       <c r="AE16" s="1">
-        <v>26.38</v>
+        <v>26.379999999999999</v>
       </c>
       <c r="AF16" s="1">
         <v>33</v>
       </c>
       <c r="AG16" s="1">
-        <v>-6.62</v>
+        <v>-6.6200000000000001</v>
       </c>
       <c r="AH16" s="1">
         <v>0</v>
@@ -2409,7 +2508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" ht="15">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -2489,7 +2588,7 @@
         <v>9653.0467293000002</v>
       </c>
       <c r="AA17" s="1">
-        <v>24.99</v>
+        <v>24.989999999999998</v>
       </c>
       <c r="AB17" s="1">
         <v>0</v>
@@ -2498,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="1">
-        <v>3.08</v>
+        <v>3.0800000000000001</v>
       </c>
       <c r="AE17" s="1">
         <v>28.07</v>
@@ -2507,7 +2606,7 @@
         <v>35</v>
       </c>
       <c r="AG17" s="1">
-        <v>-6.93</v>
+        <v>-6.9299999999999997</v>
       </c>
       <c r="AH17" s="1">
         <v>0</v>
@@ -2528,7 +2627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" ht="15">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -2608,7 +2707,7 @@
         <v>3295.2889192999996</v>
       </c>
       <c r="AA18" s="1">
-        <v>16.22</v>
+        <v>16.219999999999999</v>
       </c>
       <c r="AB18" s="1">
         <v>0</v>
@@ -2620,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="AE18" s="1">
-        <v>16.22</v>
+        <v>16.219999999999999</v>
       </c>
       <c r="AF18" s="1">
         <v>25</v>
@@ -2635,7 +2734,7 @@
         <v>17.875483599999999</v>
       </c>
       <c r="AJ18" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
       <c r="AK18" s="1">
         <v>0</v>
@@ -2644,10 +2743,10 @@
         <v>0</v>
       </c>
       <c r="AM18" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" ht="15">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -2727,7 +2826,7 @@
         <v>4888.7056763000001</v>
       </c>
       <c r="AA19" s="1">
-        <v>29.6</v>
+        <v>29.600000000000001</v>
       </c>
       <c r="AB19" s="1">
         <v>0</v>
@@ -2739,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="AE19" s="1">
-        <v>29.6</v>
+        <v>29.600000000000001</v>
       </c>
       <c r="AF19" s="1">
         <v>25</v>
@@ -2754,7 +2853,7 @@
         <v>25.297590199999998</v>
       </c>
       <c r="AJ19" s="1">
-        <v>3.6000000000000002E-4</v>
+        <v>0.00036000000000000002</v>
       </c>
       <c r="AK19" s="1">
         <v>0</v>
@@ -2763,10 +2862,10 @@
         <v>0</v>
       </c>
       <c r="AM19" s="1">
-        <v>3.6000000000000002E-4</v>
+        <v>0.00036000000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" ht="15">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -2855,16 +2954,16 @@
         <v>0</v>
       </c>
       <c r="AD20" s="1">
-        <v>5.55</v>
+        <v>5.5499999999999998</v>
       </c>
       <c r="AE20" s="1">
-        <v>70.56</v>
+        <v>70.560000000000002</v>
       </c>
       <c r="AF20" s="1">
         <v>30</v>
       </c>
       <c r="AG20" s="1">
-        <v>40.56</v>
+        <v>40.560000000000002</v>
       </c>
       <c r="AH20" s="1">
         <v>0</v>
@@ -2885,7 +2984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" ht="15">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -2965,7 +3064,7 @@
         <v>4855.3461981</v>
       </c>
       <c r="AA21" s="1">
-        <v>7.77</v>
+        <v>7.7699999999999996</v>
       </c>
       <c r="AB21" s="1">
         <v>0</v>
@@ -2974,16 +3073,16 @@
         <v>0</v>
       </c>
       <c r="AD21" s="1">
-        <v>5.78</v>
+        <v>5.7800000000000002</v>
       </c>
       <c r="AE21" s="1">
-        <v>13.55</v>
+        <v>13.550000000000001</v>
       </c>
       <c r="AF21" s="1">
         <v>30</v>
       </c>
       <c r="AG21" s="1">
-        <v>-16.45</v>
+        <v>-16.449999999999999</v>
       </c>
       <c r="AH21" s="1">
         <v>0</v>
@@ -2992,7 +3091,7 @@
         <v>28.591505300000001</v>
       </c>
       <c r="AJ21" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
       <c r="AK21" s="1">
         <v>0</v>
@@ -3001,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="AM21" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" ht="15">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -3084,7 +3183,7 @@
         <v>5566.0104368000002</v>
       </c>
       <c r="AA22" s="1">
-        <v>59.13</v>
+        <v>59.130000000000003</v>
       </c>
       <c r="AB22" s="1">
         <v>0</v>
@@ -3093,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="AD22" s="1">
-        <v>4.55</v>
+        <v>4.5499999999999998</v>
       </c>
       <c r="AE22" s="1">
         <v>63.68</v>
@@ -3102,7 +3201,7 @@
         <v>60</v>
       </c>
       <c r="AG22" s="1">
-        <v>3.68</v>
+        <v>3.6800000000000002</v>
       </c>
       <c r="AH22" s="1">
         <v>0</v>
@@ -3111,7 +3210,7 @@
         <v>27.265778900000001</v>
       </c>
       <c r="AJ22" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
       <c r="AK22" s="1">
         <v>0</v>
@@ -3120,10 +3219,10 @@
         <v>0</v>
       </c>
       <c r="AM22" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" ht="15">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3203,7 +3302,7 @@
         <v>8940.901715</v>
       </c>
       <c r="AA23" s="1">
-        <v>23.76</v>
+        <v>23.760000000000002</v>
       </c>
       <c r="AB23" s="1">
         <v>12.65</v>
@@ -3212,7 +3311,7 @@
         <v>0</v>
       </c>
       <c r="AD23" s="1">
-        <v>57.84</v>
+        <v>57.840000000000003</v>
       </c>
       <c r="AE23" s="1">
         <v>94.25</v>
@@ -3230,7 +3329,7 @@
         <v>37.119385100000002</v>
       </c>
       <c r="AJ23" s="1">
-        <v>8.8459999999999997E-2</v>
+        <v>0.088459999999999997</v>
       </c>
       <c r="AK23" s="1">
         <v>0</v>
@@ -3239,10 +3338,10 @@
         <v>0</v>
       </c>
       <c r="AM23" s="1">
-        <v>8.8459999999999997E-2</v>
+        <v>0.088459999999999997</v>
       </c>
     </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" ht="15">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3322,7 +3421,7 @@
         <v>5019.4851318999999</v>
       </c>
       <c r="AA24" s="1">
-        <v>19.78</v>
+        <v>19.780000000000001</v>
       </c>
       <c r="AB24" s="1">
         <v>15.58</v>
@@ -3334,13 +3433,13 @@
         <v>0</v>
       </c>
       <c r="AE24" s="1">
-        <v>35.36</v>
+        <v>35.359999999999999</v>
       </c>
       <c r="AF24" s="1">
         <v>45</v>
       </c>
       <c r="AG24" s="1">
-        <v>-9.64</v>
+        <v>-9.6400000000000006</v>
       </c>
       <c r="AH24" s="1">
         <v>0</v>
@@ -3361,7 +3460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" ht="15">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3441,7 +3540,7 @@
         <v>3284.3956579999995</v>
       </c>
       <c r="AA25" s="1">
-        <v>36.81</v>
+        <v>36.810000000000002</v>
       </c>
       <c r="AB25" s="1">
         <v>0</v>
@@ -3450,10 +3549,10 @@
         <v>0</v>
       </c>
       <c r="AD25" s="1">
-        <v>19.53</v>
+        <v>19.530000000000001</v>
       </c>
       <c r="AE25" s="1">
-        <v>56.34</v>
+        <v>56.340000000000003</v>
       </c>
       <c r="AF25" s="1">
         <v>25</v>
@@ -3468,7 +3567,7 @@
         <v>18.637577199999999</v>
       </c>
       <c r="AJ25" s="1">
-        <v>3.0000000000000001E-3</v>
+        <v>0.0030000000000000001</v>
       </c>
       <c r="AK25" s="1">
         <v>0</v>
@@ -3477,10 +3576,10 @@
         <v>0</v>
       </c>
       <c r="AM25" s="1">
-        <v>3.0000000000000001E-3</v>
+        <v>0.0030000000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" ht="15">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -3569,16 +3668,16 @@
         <v>0</v>
       </c>
       <c r="AD26" s="1">
-        <v>3.17</v>
+        <v>3.1699999999999999</v>
       </c>
       <c r="AE26" s="1">
-        <v>27.24</v>
+        <v>27.239999999999998</v>
       </c>
       <c r="AF26" s="1">
         <v>32</v>
       </c>
       <c r="AG26" s="1">
-        <v>-4.76</v>
+        <v>-4.7599999999999998</v>
       </c>
       <c r="AH26" s="1">
         <v>0</v>
@@ -3599,7 +3698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" ht="15">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -3679,7 +3778,7 @@
         <v>7923.4347066</v>
       </c>
       <c r="AA27" s="1">
-        <v>17.79</v>
+        <v>17.789999999999999</v>
       </c>
       <c r="AB27" s="1">
         <v>0</v>
@@ -3688,16 +3787,16 @@
         <v>0</v>
       </c>
       <c r="AD27" s="1">
-        <v>14.47</v>
+        <v>14.470000000000001</v>
       </c>
       <c r="AE27" s="1">
-        <v>32.26</v>
+        <v>32.259999999999998</v>
       </c>
       <c r="AF27" s="1">
         <v>36</v>
       </c>
       <c r="AG27" s="1">
-        <v>-3.74</v>
+        <v>-3.7400000000000002</v>
       </c>
       <c r="AH27" s="1">
         <v>0</v>
@@ -3718,7 +3817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" ht="15">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -3798,7 +3897,7 @@
         <v>6774.0171553999999</v>
       </c>
       <c r="AA28" s="1">
-        <v>13.96</v>
+        <v>13.960000000000001</v>
       </c>
       <c r="AB28" s="1">
         <v>0</v>
@@ -3807,16 +3906,16 @@
         <v>0</v>
       </c>
       <c r="AD28" s="1">
-        <v>5.09</v>
+        <v>5.0899999999999999</v>
       </c>
       <c r="AE28" s="1">
-        <v>19.05</v>
+        <v>19.050000000000001</v>
       </c>
       <c r="AF28" s="1">
         <v>30</v>
       </c>
       <c r="AG28" s="1">
-        <v>-10.95</v>
+        <v>-10.949999999999999</v>
       </c>
       <c r="AH28" s="1">
         <v>0</v>
@@ -3825,7 +3924,7 @@
         <v>37.849216200000001</v>
       </c>
       <c r="AJ28" s="1">
-        <v>3.46E-3</v>
+        <v>0.00346</v>
       </c>
       <c r="AK28" s="1">
         <v>0</v>
@@ -3834,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="AM28" s="1">
-        <v>3.46E-3</v>
+        <v>0.00346</v>
       </c>
     </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" ht="15">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -3917,7 +4016,7 @@
         <v>8654.8163055000005</v>
       </c>
       <c r="AA29" s="1">
-        <v>30.11</v>
+        <v>30.109999999999999</v>
       </c>
       <c r="AB29" s="1">
         <v>4.3899999999999997</v>
@@ -3926,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="1">
-        <v>5.16</v>
+        <v>5.1600000000000001</v>
       </c>
       <c r="AE29" s="1">
         <v>39.659999999999997</v>
@@ -3935,7 +4034,7 @@
         <v>40</v>
       </c>
       <c r="AG29" s="1">
-        <v>-0.34</v>
+        <v>-0.34000000000000002</v>
       </c>
       <c r="AH29" s="1">
         <v>0</v>
@@ -3956,7 +4055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" ht="15">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -4036,10 +4135,10 @@
         <v>9513.172553299999</v>
       </c>
       <c r="AA30" s="1">
-        <v>50.71</v>
+        <v>50.710000000000001</v>
       </c>
       <c r="AB30" s="1">
-        <v>3.8</v>
+        <v>3.7999999999999998</v>
       </c>
       <c r="AC30" s="1">
         <v>0</v>
@@ -4048,7 +4147,7 @@
         <v>0</v>
       </c>
       <c r="AE30" s="1">
-        <v>54.51</v>
+        <v>54.509999999999998</v>
       </c>
       <c r="AF30" s="1">
         <v>40</v>
@@ -4075,7 +4174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" ht="15">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -4167,13 +4266,13 @@
         <v>3.71</v>
       </c>
       <c r="AE31" s="1">
-        <v>41.3</v>
+        <v>41.299999999999997</v>
       </c>
       <c r="AF31" s="1">
         <v>30</v>
       </c>
       <c r="AG31" s="1">
-        <v>11.3</v>
+        <v>11.300000000000001</v>
       </c>
       <c r="AH31" s="1">
         <v>0</v>
@@ -4182,7 +4281,7 @@
         <v>40.716683000000003</v>
       </c>
       <c r="AJ31" s="1">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AK31" s="1">
         <v>0</v>
@@ -4191,10 +4290,10 @@
         <v>0</v>
       </c>
       <c r="AM31" s="1">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
     </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" ht="15">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -4274,7 +4373,7 @@
         <v>6209.4542081</v>
       </c>
       <c r="AA32" s="1">
-        <v>16.88</v>
+        <v>16.879999999999999</v>
       </c>
       <c r="AB32" s="1">
         <v>0</v>
@@ -4283,7 +4382,7 @@
         <v>0</v>
       </c>
       <c r="AD32" s="1">
-        <v>11.8</v>
+        <v>11.800000000000001</v>
       </c>
       <c r="AE32" s="1">
         <v>28.68</v>
@@ -4292,7 +4391,7 @@
         <v>35</v>
       </c>
       <c r="AG32" s="1">
-        <v>-6.32</v>
+        <v>-6.3200000000000003</v>
       </c>
       <c r="AH32" s="1">
         <v>0</v>
@@ -4313,7 +4412,7 @@
         <v>0.50927</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" ht="15">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -4402,10 +4501,10 @@
         <v>0</v>
       </c>
       <c r="AD33" s="1">
-        <v>7.92</v>
+        <v>7.9199999999999999</v>
       </c>
       <c r="AE33" s="1">
-        <v>31.74</v>
+        <v>31.739999999999998</v>
       </c>
       <c r="AF33" s="1">
         <v>43</v>
@@ -4420,7 +4519,7 @@
         <v>67.619299799999993</v>
       </c>
       <c r="AJ33" s="1">
-        <v>8.8999999999999995E-4</v>
+        <v>0.00088999999999999995</v>
       </c>
       <c r="AK33" s="1">
         <v>0</v>
@@ -4429,10 +4528,10 @@
         <v>0</v>
       </c>
       <c r="AM33" s="1">
-        <v>8.8999999999999995E-4</v>
+        <v>0.00088999999999999995</v>
       </c>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" ht="15">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -4512,10 +4611,10 @@
         <v>8931.9274406000004</v>
       </c>
       <c r="AA34" s="1">
-        <v>15.96</v>
+        <v>15.960000000000001</v>
       </c>
       <c r="AB34" s="1">
-        <v>13.05</v>
+        <v>13.050000000000001</v>
       </c>
       <c r="AC34" s="1">
         <v>0</v>
@@ -4524,7 +4623,7 @@
         <v>14.83</v>
       </c>
       <c r="AE34" s="1">
-        <v>43.84</v>
+        <v>43.840000000000003</v>
       </c>
       <c r="AF34" s="1">
         <v>55</v>
@@ -4539,7 +4638,7 @@
         <v>51.4659032</v>
       </c>
       <c r="AJ34" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
       <c r="AK34" s="1">
         <v>0</v>
@@ -4548,10 +4647,10 @@
         <v>0</v>
       </c>
       <c r="AM34" s="1">
-        <v>4.6000000000000001E-4</v>
+        <v>0.00046000000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" ht="15">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -4604,7 +4703,7 @@
         <v>287.55019870000001</v>
       </c>
       <c r="R35" s="3">
-        <v>3.1</v>
+        <v>3.1000000000000001</v>
       </c>
       <c r="S35" s="3">
         <v>0.91666669999999995</v>
@@ -4670,7 +4769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" ht="15">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -4750,7 +4849,7 @@
         <v>6945.7536197999998</v>
       </c>
       <c r="AA36" s="1">
-        <v>55.6</v>
+        <v>55.600000000000001</v>
       </c>
       <c r="AB36" s="1">
         <v>0</v>
@@ -4759,16 +4858,16 @@
         <v>0</v>
       </c>
       <c r="AD36" s="1">
-        <v>8.34</v>
+        <v>8.3399999999999999</v>
       </c>
       <c r="AE36" s="1">
-        <v>63.94</v>
+        <v>63.939999999999998</v>
       </c>
       <c r="AF36" s="1">
         <v>33</v>
       </c>
       <c r="AG36" s="1">
-        <v>30.94</v>
+        <v>30.940000000000001</v>
       </c>
       <c r="AH36" s="1">
         <v>0</v>
@@ -4789,7 +4888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" ht="15">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -4869,7 +4968,7 @@
         <v>10958.1427195</v>
       </c>
       <c r="AA37" s="1">
-        <v>20.76</v>
+        <v>20.760000000000002</v>
       </c>
       <c r="AB37" s="1">
         <v>0</v>
@@ -4878,16 +4977,16 @@
         <v>0</v>
       </c>
       <c r="AD37" s="1">
-        <v>5.48</v>
+        <v>5.4800000000000004</v>
       </c>
       <c r="AE37" s="1">
-        <v>26.24</v>
+        <v>26.239999999999998</v>
       </c>
       <c r="AF37" s="1">
         <v>34</v>
       </c>
       <c r="AG37" s="1">
-        <v>-7.76</v>
+        <v>-7.7599999999999998</v>
       </c>
       <c r="AH37" s="1">
         <v>0</v>
@@ -4896,7 +4995,7 @@
         <v>63.511740500000002</v>
       </c>
       <c r="AJ37" s="1">
-        <v>1.4999999999999999E-2</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="AK37" s="1">
         <v>0</v>
@@ -4905,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="AM37" s="1">
-        <v>1.4999999999999999E-2</v>
+        <v>0.014999999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" ht="15">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -4988,7 +5087,7 @@
         <v>7522.9296226000006</v>
       </c>
       <c r="AA38" s="1">
-        <v>25.89</v>
+        <v>25.890000000000001</v>
       </c>
       <c r="AB38" s="1">
         <v>0</v>
@@ -5006,7 +5105,7 @@
         <v>34</v>
       </c>
       <c r="AG38" s="1">
-        <v>0.18</v>
+        <v>0.17999999999999999</v>
       </c>
       <c r="AH38" s="1">
         <v>0</v>
@@ -5015,7 +5114,7 @@
         <v>42.7335329</v>
       </c>
       <c r="AJ38" s="1">
-        <v>2.0920000000000001E-2</v>
+        <v>0.020920000000000001</v>
       </c>
       <c r="AK38" s="1">
         <v>0</v>
@@ -5024,10 +5123,10 @@
         <v>0</v>
       </c>
       <c r="AM38" s="1">
-        <v>2.0920000000000001E-2</v>
+        <v>0.020920000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" ht="15">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -5116,16 +5215,16 @@
         <v>0</v>
       </c>
       <c r="AD39" s="1">
-        <v>-3.17</v>
+        <v>-3.1699999999999999</v>
       </c>
       <c r="AE39" s="1">
-        <v>62.58</v>
+        <v>62.579999999999998</v>
       </c>
       <c r="AF39" s="1">
         <v>38</v>
       </c>
       <c r="AG39" s="1">
-        <v>24.58</v>
+        <v>24.579999999999998</v>
       </c>
       <c r="AH39" s="1">
         <v>0</v>
@@ -5146,7 +5245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" ht="15">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -5199,7 +5298,7 @@
         <v>31.9037273</v>
       </c>
       <c r="R40" s="3">
-        <v>0.32</v>
+        <v>0.32000000000000001</v>
       </c>
       <c r="S40" s="3">
         <v>0</v>
@@ -5265,7 +5364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" ht="15">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -5354,16 +5453,16 @@
         <v>0</v>
       </c>
       <c r="AD41" s="1">
-        <v>6.01</v>
+        <v>6.0099999999999998</v>
       </c>
       <c r="AE41" s="1">
-        <v>40.06</v>
+        <v>40.060000000000002</v>
       </c>
       <c r="AF41" s="1">
         <v>33</v>
       </c>
       <c r="AG41" s="1">
-        <v>7.06</v>
+        <v>7.0599999999999996</v>
       </c>
       <c r="AH41" s="1">
         <v>0</v>
@@ -5384,7 +5483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:39" ht="15">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -5464,7 +5563,7 @@
         <v>6502.4346640000003</v>
       </c>
       <c r="AA42" s="1">
-        <v>19.04</v>
+        <v>19.039999999999999</v>
       </c>
       <c r="AB42" s="1">
         <v>16.09</v>
@@ -5503,7 +5602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:39" ht="15">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -5583,7 +5682,7 @@
         <v>11375.547760199999</v>
       </c>
       <c r="AA43" s="1">
-        <v>29.71</v>
+        <v>29.710000000000001</v>
       </c>
       <c r="AB43" s="1">
         <v>0</v>
@@ -5592,16 +5691,16 @@
         <v>0</v>
       </c>
       <c r="AD43" s="1">
-        <v>6.62</v>
+        <v>6.6200000000000001</v>
       </c>
       <c r="AE43" s="1">
-        <v>36.33</v>
+        <v>36.329999999999998</v>
       </c>
       <c r="AF43" s="1">
         <v>30</v>
       </c>
       <c r="AG43" s="1">
-        <v>6.33</v>
+        <v>6.3300000000000001</v>
       </c>
       <c r="AH43" s="1">
         <v>0</v>
@@ -5622,7 +5721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:39" ht="15">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -5675,7 +5774,7 @@
         <v>72.405174799999998</v>
       </c>
       <c r="R44" s="3">
-        <v>2.8</v>
+        <v>2.7999999999999998</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -5729,7 +5828,7 @@
         <v>26.940554500000001</v>
       </c>
       <c r="AJ44" s="1">
-        <v>5.0000000000000001E-4</v>
+        <v>0.00050000000000000001</v>
       </c>
       <c r="AK44" s="1">
         <v>0</v>
@@ -5738,10 +5837,10 @@
         <v>0</v>
       </c>
       <c r="AM44" s="1">
-        <v>5.0000000000000001E-4</v>
+        <v>0.00050000000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:39" ht="15">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -5821,7 +5920,7 @@
         <v>9825.3014743999993</v>
       </c>
       <c r="AA45" s="1">
-        <v>17.54</v>
+        <v>17.539999999999999</v>
       </c>
       <c r="AB45" s="1">
         <v>0</v>
@@ -5830,16 +5929,16 @@
         <v>0</v>
       </c>
       <c r="AD45" s="1">
-        <v>28.99</v>
+        <v>28.989999999999998</v>
       </c>
       <c r="AE45" s="1">
-        <v>46.53</v>
+        <v>46.530000000000001</v>
       </c>
       <c r="AF45" s="1">
         <v>40</v>
       </c>
       <c r="AG45" s="1">
-        <v>6.53</v>
+        <v>6.5300000000000002</v>
       </c>
       <c r="AH45" s="1">
         <v>0</v>
@@ -5860,7 +5959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:39" ht="15">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -5940,7 +6039,7 @@
         <v>6163.9818932999997</v>
       </c>
       <c r="AA46" s="1">
-        <v>30.49</v>
+        <v>30.489999999999998</v>
       </c>
       <c r="AB46" s="1">
         <v>0</v>
@@ -5958,7 +6057,7 @@
         <v>33</v>
       </c>
       <c r="AG46" s="1">
-        <v>2.34</v>
+        <v>2.3399999999999999</v>
       </c>
       <c r="AH46" s="1">
         <v>0</v>
@@ -5979,7 +6078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:39" ht="15">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -6059,7 +6158,7 @@
         <v>8635.0666188000014</v>
       </c>
       <c r="AA47" s="1">
-        <v>27.95</v>
+        <v>27.949999999999999</v>
       </c>
       <c r="AB47" s="1">
         <v>0</v>
@@ -6068,7 +6167,7 @@
         <v>0</v>
       </c>
       <c r="AD47" s="1">
-        <v>7.03</v>
+        <v>7.0300000000000002</v>
       </c>
       <c r="AE47" s="1">
         <v>34.979999999999997</v>
@@ -6098,7 +6197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:39" ht="15">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -6178,7 +6277,7 @@
         <v>8036.6742322999999</v>
       </c>
       <c r="AA48" s="1">
-        <v>21.39</v>
+        <v>21.390000000000001</v>
       </c>
       <c r="AB48" s="1">
         <v>0</v>
@@ -6187,7 +6286,7 @@
         <v>0</v>
       </c>
       <c r="AD48" s="1">
-        <v>7.88</v>
+        <v>7.8799999999999999</v>
       </c>
       <c r="AE48" s="1">
         <v>29.27</v>
@@ -6217,7 +6316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:39" ht="15">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -6297,7 +6396,7 @@
         <v>4733.1366504999996</v>
       </c>
       <c r="AA49" s="1">
-        <v>7.09</v>
+        <v>7.0899999999999999</v>
       </c>
       <c r="AB49" s="1">
         <v>0</v>
@@ -6306,7 +6405,7 @@
         <v>0</v>
       </c>
       <c r="AD49" s="1">
-        <v>7.48</v>
+        <v>7.4800000000000004</v>
       </c>
       <c r="AE49" s="1">
         <v>14.57</v>
@@ -6336,7 +6435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" ht="15">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -6434,7 +6533,7 @@
         <v>15</v>
       </c>
       <c r="AG50" s="1">
-        <v>23.37</v>
+        <v>23.370000000000001</v>
       </c>
       <c r="AH50" s="1">
         <v>0</v>
@@ -6455,7 +6554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:39" ht="15">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -6535,7 +6634,7 @@
         <v>5030.4134377</v>
       </c>
       <c r="AA51" s="1">
-        <v>19.72</v>
+        <v>19.719999999999999</v>
       </c>
       <c r="AB51" s="1">
         <v>0</v>
@@ -6544,16 +6643,16 @@
         <v>0</v>
       </c>
       <c r="AD51" s="1">
-        <v>3.47</v>
+        <v>3.4700000000000002</v>
       </c>
       <c r="AE51" s="1">
-        <v>23.19</v>
+        <v>23.190000000000001</v>
       </c>
       <c r="AF51" s="1">
         <v>25</v>
       </c>
       <c r="AG51" s="1">
-        <v>-1.81</v>
+        <v>-1.8100000000000001</v>
       </c>
       <c r="AH51" s="1">
         <v>0</v>
@@ -6574,7 +6673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:39" ht="15">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -6663,16 +6762,16 @@
         <v>0</v>
       </c>
       <c r="AD52" s="1">
-        <v>7.16</v>
+        <v>7.1600000000000001</v>
       </c>
       <c r="AE52" s="1">
-        <v>42.14</v>
+        <v>42.140000000000001</v>
       </c>
       <c r="AF52" s="1">
         <v>40</v>
       </c>
       <c r="AG52" s="1">
-        <v>2.14</v>
+        <v>2.1400000000000001</v>
       </c>
       <c r="AH52" s="1">
         <v>0</v>
@@ -6681,7 +6780,7 @@
         <v>16.588917500000001</v>
       </c>
       <c r="AJ52" s="1">
-        <v>3.4299999999999997E-2</v>
+        <v>0.034299999999999997</v>
       </c>
       <c r="AK52" s="1">
         <v>0</v>
@@ -6690,10 +6789,10 @@
         <v>0</v>
       </c>
       <c r="AM52" s="1">
-        <v>3.4299999999999997E-2</v>
+        <v>0.034299999999999997</v>
       </c>
     </row>
-    <row r="53" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:39" ht="15">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -6782,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="AD53" s="1">
-        <v>6.77</v>
+        <v>6.7699999999999996</v>
       </c>
       <c r="AE53" s="1">
         <v>25.25</v>
@@ -6812,7 +6911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:39" ht="15">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -6892,7 +6991,7 @@
         <v>6112.2302569000003</v>
       </c>
       <c r="AA54" s="1">
-        <v>21.05</v>
+        <v>21.050000000000001</v>
       </c>
       <c r="AB54" s="1">
         <v>0</v>
@@ -6904,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="AE54" s="1">
-        <v>21.05</v>
+        <v>21.050000000000001</v>
       </c>
       <c r="AF54" s="1">
         <v>23</v>
@@ -6931,7 +7030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:39" ht="15">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -7011,7 +7110,7 @@
         <v>4285.8890275000003</v>
       </c>
       <c r="AA55" s="1">
-        <v>4.03</v>
+        <v>4.0300000000000002</v>
       </c>
       <c r="AB55" s="1">
         <v>0</v>
@@ -7020,10 +7119,10 @@
         <v>0</v>
       </c>
       <c r="AD55" s="1">
-        <v>2.16</v>
+        <v>2.1600000000000001</v>
       </c>
       <c r="AE55" s="1">
-        <v>6.19</v>
+        <v>6.1900000000000004</v>
       </c>
       <c r="AF55" s="1">
         <v>23</v>
@@ -7050,7 +7149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:39" ht="15">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -7067,7 +7166,7 @@
         <v>969.12999319999994</v>
       </c>
       <c r="F56" s="3">
-        <v>85.36</v>
+        <v>85.359999999999999</v>
       </c>
       <c r="G56" s="3">
         <v>1054.4899931999998</v>
@@ -7103,7 +7202,7 @@
         <v>0</v>
       </c>
       <c r="R56" s="3">
-        <v>4.42</v>
+        <v>4.4199999999999999</v>
       </c>
       <c r="S56" s="3">
         <v>0</v>
@@ -7142,13 +7241,13 @@
         <v>4.6500000000000004</v>
       </c>
       <c r="AE56" s="1">
-        <v>16.13</v>
+        <v>16.129999999999999</v>
       </c>
       <c r="AF56" s="1">
         <v>20</v>
       </c>
       <c r="AG56" s="1">
-        <v>-3.87</v>
+        <v>-3.8700000000000001</v>
       </c>
       <c r="AH56" s="1">
         <v>0</v>
@@ -7169,7 +7268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:39" ht="15">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -7183,13 +7282,13 @@
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>71.09</v>
+        <v>71.090000000000003</v>
       </c>
       <c r="F57" s="1">
         <v>13.31</v>
       </c>
       <c r="G57" s="1">
-        <v>84.4</v>
+        <v>84.400000000000006</v>
       </c>
       <c r="H57" s="1">
         <v>0</v>
@@ -7290,5 +7389,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>